--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104649_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104649_W22.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2857</v>
+        <v>7.1532</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3965</v>
+        <v>4.7869</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8892</v>
+        <v>2.3664</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6905</v>
+        <v>3.6977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.857</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8335</v>
+        <v>2.8364</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0757</v>
+        <v>4.0522</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2051</v>
+        <v>1.1926</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8707</v>
+        <v>2.8596</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3852</v>
+        <v>-0.3544</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.539</v>
+        <v>-0.6827</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0253</v>
+        <v>-0.602</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4863</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1962</v>
+        <v>5.8989</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4697</v>
+        <v>4.8909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7265</v>
+        <v>1.0079</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4431</v>
+        <v>6.4252</v>
       </c>
       <c r="H3" t="n">
         <v>2.6796</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7636</v>
+        <v>3.7456</v>
       </c>
       <c r="J3" t="n">
-        <v>7.172</v>
+        <v>7.1272</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0753</v>
+        <v>3.0542</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0967</v>
+        <v>4.073</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7289</v>
+        <v>-0.702</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3957</v>
+        <v>-0.3745</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7687</v>
+        <v>-1.0499</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1825</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5861</v>
+        <v>-0.3388</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7291</v>
+        <v>1.2999</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4536</v>
+        <v>1.4961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2755</v>
+        <v>-0.1962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5774</v>
+        <v>0.587</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3317</v>
+        <v>1.3408</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7543</v>
+        <v>-0.7537</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8589</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2921</v>
+        <v>-0.2719</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4959</v>
+        <v>0.0512</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8771</v>
+        <v>-0.0653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6188</v>
+        <v>0.1165</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2698</v>
+        <v>0.8166</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7648</v>
+        <v>-1.187</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0346</v>
+        <v>2.0035</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5441</v>
+        <v>-0.5222</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9467</v>
+        <v>-0.9368</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4026</v>
+        <v>0.4146</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4066</v>
+        <v>-0.4111</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1375</v>
+        <v>-0.1111</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2353</v>
+        <v>-0.7036</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1785</v>
+        <v>-0.2232</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4138</v>
+        <v>-0.4804</v>
       </c>
       <c r="V5" t="n">
-        <v>2.9566</v>
+        <v>2.9529</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2678</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3062</v>
+        <v>0.0306</v>
       </c>
       <c r="F6" t="n">
-        <v>0.574</v>
+        <v>0.7198</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3185</v>
+        <v>1.3242</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7836</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5437</v>
+        <v>0.5406</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3629</v>
+        <v>1.3527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0444</v>
+        <v>-0.0285</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0507</v>
+        <v>-0.5737</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3551</v>
+        <v>-0.232</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1422</v>
+        <v>0.2451</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9557</v>
+        <v>-0.0741</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0979</v>
+        <v>0.3192</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0588</v>
+        <v>3.8091</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9709</v>
+        <v>2.7947</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08790000000000001</v>
+        <v>1.0144</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4204</v>
+        <v>4.0072</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.607</v>
+        <v>3.2405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1866</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6384</v>
+        <v>-0.1981</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3639</v>
+        <v>-0.4458</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-3.8697</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6152</v>
+        <v>-0.8128</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5989</v>
+        <v>-0.2115</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0163</v>
+        <v>-0.6012</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3214</v>
+        <v>-0.7025</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3214</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1194</v>
+        <v>-0.6925</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2216</v>
+        <v>-1.6979</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1022</v>
+        <v>1.0054</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8135</v>
+        <v>-1.0692</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7979</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0156</v>
+        <v>-0.0848</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0338</v>
+        <v>-0.4526</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2555</v>
+        <v>-0.6387</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7782</v>
+        <v>0.1862</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2203</v>
+        <v>-0.6166</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4576</v>
+        <v>-0.3457</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2373</v>
+        <v>-0.271</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8562</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1844</v>
+        <v>-0.2184</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3992</v>
+        <v>-0.1072</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7852</v>
+        <v>-0.1111</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7071</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5768</v>
+        <v>-1.4019</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9982</v>
+        <v>-2.0098</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4214</v>
+        <v>0.6079</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5169</v>
+        <v>0.5352</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1789</v>
+        <v>-1.3729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6957</v>
+        <v>1.9081</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9416</v>
+        <v>1.1634</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1487</v>
+        <v>-0.8693</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0903</v>
+        <v>2.0327</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4247</v>
+        <v>-0.6282</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0301</v>
+        <v>-0.5036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3946</v>
+        <v>-0.1246</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5878</v>
+        <v>-2.7316</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.126</v>
+        <v>-1.2542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.4416</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6572</v>
+        <v>-0.8126</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.948</v>
+        <v>-1.411</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2745</v>
+        <v>-2.9548</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3265</v>
+        <v>1.5439</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5375</v>
+        <v>-0.5137</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3737</v>
+        <v>0.1836</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9112</v>
+        <v>-0.6972</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1945</v>
+        <v>-0.9617</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8525</v>
+        <v>0.1411</v>
       </c>
       <c r="L10" t="n">
-        <v>2.047</v>
+        <v>-1.1029</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.657</v>
+        <v>0.4481</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5212</v>
+        <v>0.0424</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1359</v>
+        <v>0.4057</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.722</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.805</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.747</v>
+        <v>-0.3997</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.058</v>
+        <v>-0.5675</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9971</v>
+        <v>-2.0599</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1238</v>
+        <v>-2.5603</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1267</v>
+        <v>0.5004</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2381</v>
+        <v>-2.2326</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5557</v>
+        <v>-1.5457</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6824</v>
+        <v>-0.6869</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0374</v>
+        <v>-1.0569</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8454</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2007</v>
+        <v>-1.1758</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8271</v>
+        <v>-0.8955</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.113</v>
+        <v>-0.523</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7141</v>
+        <v>-0.3725</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.2495</v>
+        <v>10.5989</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6749999999999994</v>
+        <v>0.7206000000000023</v>
       </c>
       <c r="F12" t="n">
-        <v>9.5745</v>
+        <v>9.8782</v>
       </c>
       <c r="G12" t="n">
-        <v>12.0226</v>
+        <v>12.0407</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7728</v>
+        <v>3.803900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>8.249899999999998</v>
+        <v>8.2371</v>
       </c>
       <c r="J12" t="n">
-        <v>15.9024</v>
+        <v>15.6793</v>
       </c>
       <c r="K12" t="n">
-        <v>7.173600000000002</v>
+        <v>7.0438</v>
       </c>
       <c r="L12" t="n">
-        <v>8.7288</v>
+        <v>8.635600000000002</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8798</v>
+        <v>-3.6385</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.4008</v>
+        <v>-3.2399</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4791000000000001</v>
+        <v>-0.3987</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4024</v>
+        <v>3.414299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8785</v>
+        <v>-15.9344</v>
       </c>
       <c r="R12" t="n">
-        <v>19.2809</v>
+        <v>19.3489</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.4251</v>
+        <v>-7.1068</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.9769</v>
+        <v>-3.6264</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4481</v>
+        <v>-3.4803</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2495</v>
+        <v>2.250400000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.6279</v>
+        <v>4.602</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3784</v>
+        <v>-2.3517</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3803</v>
+        <v>5.5314</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7376</v>
+        <v>4.7037</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6427</v>
+        <v>0.8277</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9781</v>
+        <v>0.9694</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3997</v>
+        <v>0.3992</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5784</v>
+        <v>0.5702</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3738</v>
+        <v>2.3439</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1878</v>
+        <v>1.1754</v>
       </c>
       <c r="L13" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3957</v>
+        <v>-1.3745</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6291</v>
+        <v>0.7896</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1785</v>
+        <v>0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4506</v>
+        <v>0.6088</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5103</v>
+        <v>1.212</v>
       </c>
       <c r="E14" t="n">
-        <v>2.499</v>
+        <v>1.1628</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0112</v>
+        <v>0.0492</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4147</v>
+        <v>0.4058</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0434</v>
+        <v>2.0339</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6286</v>
+        <v>-1.6281</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5908</v>
+        <v>3.5581</v>
       </c>
       <c r="K14" t="n">
-        <v>3.335</v>
+        <v>3.3127</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.1761</v>
+        <v>-3.1522</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>2.778</v>
+        <v>1.4875</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3107</v>
+        <v>1.0192</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4673</v>
+        <v>0.4683</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6182</v>
+        <v>0.2925</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9059</v>
+        <v>0.5441</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2877</v>
+        <v>-0.2516</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5252</v>
+        <v>-0.5283</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5252</v>
+        <v>-0.5283</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0102</v>
+        <v>0.0033</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0102</v>
+        <v>0.0033</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7558</v>
+        <v>0.4354</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7349</v>
+        <v>0.3831</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. KUATH</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2683</v>
+        <v>0.2292</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6318</v>
+        <v>-1.3106</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3635</v>
+        <v>1.5398</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0668</v>
+        <v>-0.4621</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0028</v>
+        <v>0.0233</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0639</v>
+        <v>-0.4854</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2363</v>
+        <v>1.5991</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1243</v>
+        <v>0.5269</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>1.0722</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.303</v>
+        <v>-2.0612</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1272</v>
+        <v>-0.5036</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1759</v>
+        <v>-1.5576</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3993</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8207</v>
+        <v>0.1877</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5786</v>
+        <v>0.7101</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1568</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>K. KUATH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0354</v>
+        <v>-1.0049</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5663</v>
+        <v>-0.5702</v>
       </c>
       <c r="F17" t="n">
-        <v>1.531</v>
+        <v>-0.4346</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4615</v>
+        <v>-0.0634</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0289</v>
+        <v>-0.0056</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4904</v>
+        <v>-0.0578</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6296</v>
+        <v>0.2216</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5501</v>
+        <v>0.1099</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0795</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0911</v>
+        <v>-0.2851</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5212</v>
+        <v>-0.1155</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5699</v>
+        <v>-0.1695</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3717</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.113</v>
+        <v>0.6454</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7413</v>
+        <v>0.4846</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.1609</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4409</v>
+        <v>-1.4526</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.794</v>
+        <v>-2.0412</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3531</v>
+        <v>0.5886</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8173</v>
+        <v>-1.8107</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2655</v>
+        <v>-1.2611</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4315</v>
+        <v>-1.4386</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3064</v>
+        <v>0.2914</v>
       </c>
       <c r="T18" t="n">
-        <v>0.248</v>
+        <v>0.0136</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0584</v>
+        <v>0.2777</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1948</v>
+        <v>-1.551</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0459</v>
+        <v>-2.7043</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8512</v>
+        <v>1.1533</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6688</v>
+        <v>-2.2083</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7675</v>
+        <v>-1.2401</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2162</v>
+        <v>-1.0036</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2162</v>
+        <v>0.4267</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.4303</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4526</v>
+        <v>-1.2047</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5513</v>
+        <v>-1.6668</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.4622</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6082</v>
+        <v>0.202</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4386</v>
+        <v>-0.3349</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1697</v>
+        <v>0.5369</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3471</v>
+        <v>-2.382</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3714</v>
+        <v>-0.0116</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0244</v>
+        <v>-2.3704</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1995</v>
+        <v>0.3371</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2292</v>
+        <v>-0.4449</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9702</v>
+        <v>0.782</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.967</v>
+        <v>2.2535</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4565</v>
+        <v>-0.3005</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4234</v>
+        <v>2.554</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2325</v>
+        <v>-1.9164</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6857</v>
+        <v>-0.1444</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4532</v>
+        <v>-1.772</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6012999999999999</v>
+        <v>0.6875</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0434</v>
+        <v>0.2388</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4422</v>
+        <v>0.4487</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0825</v>
+        <v>-2.4715</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3247</v>
+        <v>-3.3034</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7577</v>
+        <v>0.8319</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3436</v>
+        <v>-1.6759</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.44</v>
+        <v>-1.7773</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7837</v>
+        <v>0.1014</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2884</v>
+        <v>-1.2313</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2811</v>
+        <v>-1.2313</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5694</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9447</v>
+        <v>-0.4446</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.159</v>
+        <v>-0.546</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7858</v>
+        <v>0.1014</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0139</v>
+        <v>0.3425</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1179</v>
+        <v>0.2042</v>
       </c>
       <c r="U21" t="n">
-        <v>0.104</v>
+        <v>0.1383</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5938</v>
+        <v>-3.1496</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1168</v>
+        <v>-1.0055</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.477</v>
+        <v>-2.1441</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6947</v>
+        <v>-2.6872</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0375</v>
+        <v>0.0401</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7321</v>
+        <v>-2.7273</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1198</v>
+        <v>-1.1284</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5749</v>
+        <v>-1.5588</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0333</v>
+        <v>0.3995</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2299</v>
+        <v>0.3505</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2631</v>
+        <v>0.049</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3323</v>
+        <v>-4.7144</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2903</v>
+        <v>-5.4999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.958</v>
+        <v>0.7855</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3253</v>
+        <v>-4.3173</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0521</v>
+        <v>-1.0431</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.2733</v>
+        <v>-3.2742</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5147</v>
+        <v>-1.539</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2873</v>
+        <v>0.279</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.802</v>
+        <v>-1.818</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8106</v>
+        <v>-2.7783</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4712</v>
+        <v>-1.4562</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9684</v>
+        <v>1.5817</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2389</v>
+        <v>0.5917</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2073</v>
+        <v>0.99</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.2497</v>
+        <v>-9.460899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.735099999999999</v>
+        <v>-10.0361</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5143000000000002</v>
+        <v>0.5753</v>
       </c>
       <c r="G24" t="n">
-        <v>-12.0227</v>
+        <v>-12.0409</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.772799999999999</v>
+        <v>-3.803900000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.249500000000001</v>
+        <v>-8.237</v>
       </c>
       <c r="J24" t="n">
-        <v>3.879900000000001</v>
+        <v>3.6386</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4006</v>
+        <v>3.2399</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4792999999999994</v>
+        <v>0.3987000000000003</v>
       </c>
       <c r="M24" t="n">
-        <v>-15.9024</v>
+        <v>-15.6793</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.173699999999999</v>
+        <v>-7.043699999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.728900000000001</v>
+        <v>-8.6356</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.402600000000001</v>
+        <v>-3.4146</v>
       </c>
       <c r="Q24" t="n">
-        <v>-19.2808</v>
+        <v>-19.3486</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8785</v>
+        <v>15.9343</v>
       </c>
       <c r="S24" t="n">
-        <v>7.425000000000001</v>
+        <v>8.2448</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4481</v>
+        <v>3.4801</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9772</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2495</v>
+        <v>-2.2505</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2176</v>
+        <v>2.1938</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.467300000000001</v>
+        <v>-4.4443</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104649_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104649_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-2.3517</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104649_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.4443</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
